--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_depmenores_a_2021_o_higgins.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_depmenores_a_2021_o_higgins.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:30</t>
+    <t xml:space="preserve">2026-09-24 01:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -561,19 +561,19 @@
         <v>8</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>-0.16</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.84</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="3">
@@ -584,19 +584,19 @@
         <v>8</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>-0.23</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.88</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="4">
@@ -607,19 +607,19 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>-0.2</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="5">
@@ -630,16 +630,16 @@
         <v>8</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>-0.55</v>
+        <v>-0.56</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>-0.6</v>
@@ -653,19 +653,19 @@
         <v>8</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>-0.58</v>
+        <v>-0.5</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>0.09</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>-0.67</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="7">
@@ -676,19 +676,19 @@
         <v>14</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="8">
@@ -699,19 +699,19 @@
         <v>14</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>0.12</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.07</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="9">
@@ -722,19 +722,19 @@
         <v>14</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>0.17</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="10">
@@ -745,19 +745,19 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>-0.01</v>
+        <v>-0.09</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>0.16</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="11">
@@ -768,19 +768,19 @@
         <v>14</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>0.16</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="12">
@@ -794,13 +794,13 @@
         <v>-0.21</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>0.21</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>-0.42</v>
@@ -814,19 +814,19 @@
         <v>14</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>-0.07</v>
+        <v>-0.05</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>0.19</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>-0.26</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="14">
@@ -837,19 +837,19 @@
         <v>14</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>-0.35</v>
+        <v>-0.38</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>-0.02</v>
+        <v>0.15</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>-0.33</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="15">
@@ -860,19 +860,19 @@
         <v>14</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>0.06</v>
+        <v>0.14</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.03</v>
+        <v>0.14</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -883,19 +883,19 @@
         <v>14</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>-0.28</v>
+        <v>-0.19</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.66</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="17">
@@ -906,19 +906,19 @@
         <v>14</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.26</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.65</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="18">
@@ -929,19 +929,19 @@
         <v>26</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>-0.22</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="19">
@@ -952,19 +952,19 @@
         <v>28</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>-0.23</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.34</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="20">
@@ -978,13 +978,13 @@
         <v>0.24</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>-0.35</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>0.59</v>
@@ -998,19 +998,19 @@
         <v>31</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>-0.09</v>
+        <v>0.13</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.25</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="22">
@@ -1021,19 +1021,19 @@
         <v>31</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>0.26</v>
+        <v>0.22</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.17</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.3</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="23">
@@ -1044,19 +1044,19 @@
         <v>31</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>0.09</v>
+        <v>0.07</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>-0.19</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
     </row>
   </sheetData>
